--- a/per-stock/CIEN/financials.xlsx
+++ b/per-stock/CIEN/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>78399774720</v>
+        <v>60615794688</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78689763328</v>
+        <v>60993540096</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>357.71616</v>
+        <v>142.74</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64.0852</v>
+        <v>44.51717</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15.29964</v>
+        <v>10.88421</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -606,7 +615,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.42125</v>
+        <v>0.43047002</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -621,7 +630,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.13399</v>
+        <v>0.15195</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -636,7 +645,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.044699997</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -651,7 +660,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08201</v>
+        <v>0.15464</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -666,7 +675,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.331</v>
+        <v>0.395</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -681,7 +690,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1299728000</v>
+        <v>1202834048</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -696,7 +705,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1589719040</v>
+        <v>1580579968</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>699300736</v>
+        <v>832659000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -726,7 +735,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>141398427</v>
+        <v>141552922</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>554.46</v>
+        <v>428.22</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-04-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D54</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C54</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B54</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B53:E53)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D52</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C52</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B52</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B51:E51)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D41</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C41</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B41</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B40:E40)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B7:E7)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D4</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C4</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B4</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B4</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D2/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C2/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1914,13 +2394,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1930,6 +2410,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1940,30 +2421,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
@@ -1976,21 +2462,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>73908.075824</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-937310.504376</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-22129380</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-665036.569987</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>-1187550</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-1367902.90696</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1999,21 +2486,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.05557</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.170234</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.235661</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>0.350206</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2022,21 +2510,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>297016000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>251705000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>167550000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>127132000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>82094000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>129374000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2045,21 +2534,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>1330000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-5506000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-105378000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-2822000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>-5655000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>-3906000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2068,21 +2558,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>1330000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-5506000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-105378000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-2822000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-5655000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>-3906000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2091,21 +2582,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>218220000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>150283000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>19489000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>50308000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>8969000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>44572000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2114,21 +2606,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>45211000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>43830000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>37358000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>35654000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>33869000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>33457000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2137,21 +2630,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>837687000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>762428000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>743559000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>687208000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>645716000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>573527000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2160,21 +2654,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>298346000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>246199000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>62172000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>124310000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>76439000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>125468000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2183,21 +2678,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>253135000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>202369000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>24814000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>88656000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>42570000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>92011000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2206,21 +2702,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-8946000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-4595000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-10254000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-6664000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-10119000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-9707000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2229,21 +2726,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>22075000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>21254000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>21956000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>22837000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>23554000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>23417000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2252,21 +2750,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>13129000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>16659000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>11702000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>16173000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>13435000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>13710000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2275,21 +2774,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>216963908.075824</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>154851689.495624</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>102737620</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>52464963.430013</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>13436450</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>47110097.09304</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2298,21 +2798,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>218220000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>150283000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>19489000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>50308000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>8969000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>44572000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2321,21 +2822,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>1332063000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>1235826000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>1233494000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>1144080000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>1091088000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>990053000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2344,21 +2846,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>237871000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>189412000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>10491000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>73535000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>32842000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>80663000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2367,21 +2870,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>146314000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>145799000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>145470000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>144499000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>144972000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>145944000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2390,21 +2894,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>141949000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>141676000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>141527000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>141846000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>142503000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>142880000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2413,21 +2918,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>0.13</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>0.06</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>0.31</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2436,21 +2942,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>0.14</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>0.06</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>0.31</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2459,21 +2966,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>218220000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>150283000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>19489000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>50308000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>8969000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>44572000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2482,21 +2990,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>218220000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>150283000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>19489000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>50308000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>8969000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>44572000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2505,21 +3014,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>218220000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>150283000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>19489000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>50308000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>8969000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>44572000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2528,21 +3038,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>218220000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>150283000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>19489000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>50308000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>8969000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>44572000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2551,21 +3062,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>218220000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>150283000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>19489000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>50308000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>8969000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>44572000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2574,21 +3086,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>12840000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>30832000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>-16631000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>15511000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>10047000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>24022000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2597,21 +3110,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>231060000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>181115000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>2858000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>65819000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>19016000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>68594000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2620,21 +3134,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>1330000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-5506000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-105378000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-2822000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-5655000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>-3906000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2646,10 +3161,11 @@
       <c r="C31" s="3" t="n"/>
       <c r="D31" s="3" t="n"/>
       <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n">
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n">
         <v>-499000</v>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="H31" s="3" t="n">
         <v>-433000</v>
       </c>
     </row>
@@ -2660,21 +3176,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-805000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>-1804000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>-107999000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>-1770000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>-1948000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>-2273000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2683,15 +3200,16 @@
         </is>
       </c>
       <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n">
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="3" t="n"/>
       <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n">
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n">
         <v>729000</v>
       </c>
-      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2700,21 +3218,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>805000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>1498000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>106851000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>1770000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>1948000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>1544000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2723,9 +3242,11 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>306000</v>
       </c>
-      <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="n"/>
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="n">
@@ -2734,6 +3255,9 @@
       <c r="G35" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H35" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2742,21 +3266,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>2135000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>-3702000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>2621000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>-1052000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>-3707000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>-1633000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2765,21 +3290,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>-8946000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>-4595000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>-10254000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>-6664000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>-10119000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>-9707000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2788,21 +3314,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>22075000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>21254000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>21956000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>22837000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>23554000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>23417000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2811,21 +3338,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>13129000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>16659000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>11702000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>16173000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>13435000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>13710000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2834,21 +3362,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>238676000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>191216000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>118490000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>75305000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>34790000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>82207000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2857,21 +3386,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>452878000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>434304000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>458689000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>427774000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>418048000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>389614000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2880,21 +3410,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>3713000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>4736000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>6112000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>6556000</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>6545000</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>6545000</v>
       </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2903,21 +3434,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>3713000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>4736000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>6112000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>6556000</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>6545000</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>6545000</v>
       </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2926,21 +3458,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>3713000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>4736000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>6112000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>6556000</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>6545000</v>
       </c>
       <c r="F44" s="3" t="n">
         <v>6545000</v>
       </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2949,21 +3482,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>3713000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>4736000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>6112000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>6556000</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>6545000</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>6545000</v>
       </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2972,21 +3506,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>237905000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>221458000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>228900000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>211898000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>214868000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>192663000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2995,21 +3530,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>211260000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>208110000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>223677000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>209320000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>196635000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>190406000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3018,21 +3554,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>150039000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>148867000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>156420000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>148724000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>139683000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>136504000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3041,21 +3578,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>61221000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>59243000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>67257000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>60596000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>56952000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>53902000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3064,21 +3602,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>61221000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>59243000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>67257000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>60596000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>56952000</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>53902000</v>
-      </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3087,21 +3626,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>691554000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>625520000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>577179000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>503079000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>452838000</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>471821000</v>
-      </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3110,21 +3650,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>879185000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>801522000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>774805000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>716306000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>673040000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>600439000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3133,21 +3674,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>1570739000</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>1427042000</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="D53" s="3" t="n">
         <v>1351984000</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>1219385000</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="F53" s="3" t="n">
         <v>1125878000</v>
       </c>
-      <c r="F53" s="3" t="n">
-        <v>1072260000</v>
-      </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3156,28 +3698,29 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
+        <v>1570739000</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>1427042000</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>1351984000</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>1219385000</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="F54" s="3" t="n">
         <v>1125878000</v>
       </c>
-      <c r="F54" s="3" t="n">
-        <v>1072260000</v>
-      </c>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5017,7 +5560,2025 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G91"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>141597550</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>141452656</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>141016300</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>141342527</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>141686082</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>141597550</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>141452656</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>141016300</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>141342527</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>141686082</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>485993000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>412911000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>443786000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>482071000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>590585000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1580580000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1588665000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1625554000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1587239000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1588629000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>2169634000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>2057957000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1983909000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>2203800000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>2184115000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>4423344000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>4328682000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>4265061000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>4325348000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>4316735000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>2259583000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>2282504000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>2257113000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>2562744000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>2517265000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>2169634000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>2057957000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1983909000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>2203800000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>2184115000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>49461000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>52341000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>89816000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>49192000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>48273000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>2892225000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>2792358000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>2729323000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>2787301000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>2776379000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>4411764000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>4317102000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>4253481000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>4313768000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>4305155000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>2892225000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>2792358000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>2729323000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>2787301000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>2776379000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>2892225000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>2792358000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>2729323000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>2787301000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>2776379000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-40081000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-38723000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-55035000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-44829000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-39596000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-40081000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-38723000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-55035000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-44829000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-39596000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-2801606000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-3019826000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-3170109000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-3189598000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-3239906000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>5732496000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>5849492000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>5953057000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>6020315000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>6054464000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>1416000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>1415000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>1410000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>1413000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>1417000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1416000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1415000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1410000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>1413000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>1417000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>3147224000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>3100001000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>3135344000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>2961477000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>2882987000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>1838643000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>1841628000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1826950000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>1837998000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>1835927000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>185001000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>182329000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>11564000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>195976000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>188809000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Derivative Product Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n">
+        <v>1345000</v>
+      </c>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Tradeand Other Payables Non Current</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n">
+        <v>102718000</v>
+      </c>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n">
+        <v>113365000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>102107000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>100455000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>116046000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>81057000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>83239000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>102107000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>100455000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>94850000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>81057000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>83239000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>1551535000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1558844000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1595277000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>1560965000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1563879000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>31996000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>34100000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>71119000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>34498000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>35103000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>1519539000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>1524744000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>1524158000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>1526467000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>1528776000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>1308581000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>1258373000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1308394000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>1123479000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>1047060000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>158972000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>129068000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>138727000</v>
+      </c>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n">
+        <v>113030000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>238380000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>290418000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>208936000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>196209000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>221835000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>238380000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>290418000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>208936000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>196209000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>221835000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>29045000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>29821000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>30277000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>26274000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>24750000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>17465000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>18241000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>18697000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>14694000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>13170000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>11580000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>11580000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>11580000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>11580000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>11580000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>11580000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>11580000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>11580000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>11580000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>11580000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>36010000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>33176000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>33708000</v>
+      </c>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="3" t="n">
+        <v>31250000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Current Provisions</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>60356000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>58084000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>55533000</v>
+      </c>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n">
+        <v>55267000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>785818000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>717806000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>841213000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>900996000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>800475000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>5992000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>9833000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>6101000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>436312000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>381398000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Interest Payable</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>5992000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>9833000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>6101000</v>
+      </c>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n">
+        <v>6120000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>779826000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>707973000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>835112000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>464684000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>419077000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>173227000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>160752000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>292271000</v>
+      </c>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n">
+        <v>183843000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Income Tax Payable</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>659000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>8529000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>10729000</v>
+      </c>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n">
+        <v>35111000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>606599000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>547221000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>542841000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>464684000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>419077000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>6039449000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>5892359000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>5864667000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>5748778000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>5659366000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>2471285000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>2351482000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>2299160000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>2062555000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>2095041000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>191068000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>190888000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>105667000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>154059000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>159081000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>873979000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>877995000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>915200000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>851903000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>863571000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>873979000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>877995000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>884889000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>851903000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>863571000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Non Current Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n"/>
+      <c r="C54" s="3" t="n"/>
+      <c r="D54" s="3" t="n">
+        <v>28610000</v>
+      </c>
+      <c r="E54" s="3" t="n"/>
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Financial Assets</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n">
+        <v>11777000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>200106000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>69876000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>78877000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>64397000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>92121000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Other Investments</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n"/>
+      <c r="D57" s="3" t="n"/>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="n">
+        <v>80920000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Investmentin Financial Assets</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>200106000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>69876000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>57142000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>64397000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>92121000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Available For Sale Securities</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>200106000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>69876000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>57142000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>64397000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>92121000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Long Term Equity Investment</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" s="3" t="n">
+        <v>21735000</v>
+      </c>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n">
+        <v>21730000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Investments In Other Ventures Under Equity Method</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n"/>
+      <c r="C61" s="3" t="n"/>
+      <c r="D61" s="3" t="n">
+        <v>21735000</v>
+      </c>
+      <c r="E61" s="3" t="n"/>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="3" t="n">
+        <v>21730000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>722591000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>734401000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>745414000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>583501000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>592264000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>202190000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>212689000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>224210000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>138673000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>147459000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>520401000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>521712000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>521204000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>444828000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>444805000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>483541000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>478322000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>425392000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>408695000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>388004000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n"/>
+      <c r="C66" s="3" t="n"/>
+      <c r="D66" s="3" t="n">
+        <v>-664248000</v>
+      </c>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="3" t="n">
+        <v>-596027000</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>483541000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>478322000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>1089640000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>408695000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>388004000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n"/>
+      <c r="C68" s="3" t="n"/>
+      <c r="D68" s="3" t="n">
+        <v>91562000</v>
+      </c>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="3" t="n"/>
+      <c r="G68" s="3" t="n">
+        <v>77451000</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>483541000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>478322000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>38613000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>408695000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>388004000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n"/>
+      <c r="C70" s="3" t="n"/>
+      <c r="D70" s="3" t="n">
+        <v>892223000</v>
+      </c>
+      <c r="E70" s="3" t="n"/>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="3" t="n">
+        <v>788781000</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n"/>
+      <c r="D71" s="3" t="n">
+        <v>67242000</v>
+      </c>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3" t="n">
+        <v>67517000</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n"/>
+      <c r="C72" s="3" t="n"/>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>3568164000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>3540877000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>3565507000</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>3686223000</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>3564325000</v>
+      </c>
+      <c r="G73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>504314000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>427918000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>47452000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>473901000</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>506252000</v>
+      </c>
+      <c r="G74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Hedging Assets Current</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="3" t="n"/>
+      <c r="D75" s="3" t="n">
+        <v>3236000</v>
+      </c>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="n"/>
+      <c r="G75" s="3" t="n">
+        <v>2149000</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n"/>
+      <c r="C76" s="3" t="n"/>
+      <c r="D76" s="3" t="n">
+        <v>37836000</v>
+      </c>
+      <c r="E76" s="3" t="n"/>
+      <c r="F76" s="3" t="n"/>
+      <c r="G76" s="3" t="n">
+        <v>20906000</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n"/>
+      <c r="C77" s="3" t="n"/>
+      <c r="D77" s="3" t="n">
+        <v>145870000</v>
+      </c>
+      <c r="E77" s="3" t="n"/>
+      <c r="F77" s="3" t="n"/>
+      <c r="G77" s="3" t="n">
+        <v>324029000</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>808447000</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>845823000</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>826235000</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>860403000</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>874326000</v>
+      </c>
+      <c r="G78" s="3" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Inventories Adjustments Allowances</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>-156735000</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>-145943000</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>-129408000</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>-121477000</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>-118021000</v>
+      </c>
+      <c r="G79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Other Inventories</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>44050000</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>43213000</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>40759000</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>41831000</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>36663000</v>
+      </c>
+      <c r="G80" s="3" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>334488000</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>318547000</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>286050000</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>261732000</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>273376000</v>
+      </c>
+      <c r="G81" s="3" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>40187000</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>33998000</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>35051000</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>35611000</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>35317000</v>
+      </c>
+      <c r="G82" s="3" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>546457000</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>596008000</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>593783000</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>642706000</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>646991000</v>
+      </c>
+      <c r="G83" s="3" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>1052569000</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>967408000</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>1196778000</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>1025563000</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>929799000</v>
+      </c>
+      <c r="G84" s="3" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n"/>
+      <c r="C85" s="3" t="n"/>
+      <c r="D85" s="3" t="n">
+        <v>220922000</v>
+      </c>
+      <c r="E85" s="3" t="n"/>
+      <c r="F85" s="3" t="n"/>
+      <c r="G85" s="3" t="n">
+        <v>173854000</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>1052569000</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>967408000</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>975856000</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>1025563000</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>929799000</v>
+      </c>
+      <c r="G86" s="3" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>-11000000</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>-11200000</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>-11212000</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>-9500000</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>-9800000</v>
+      </c>
+      <c r="G87" s="3" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>1063569000</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>978608000</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>987068000</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>1035063000</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>939599000</v>
+      </c>
+      <c r="G88" s="3" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>1202834000</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>1299728000</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>1308100000</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>1326356000</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>1253948000</v>
+      </c>
+      <c r="G89" s="3" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>157708000</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>176315000</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>216148000</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>270380000</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>304177000</v>
+      </c>
+      <c r="G90" s="3" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>1045126000</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>1123413000</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>1091952000</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>1055976000</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>949771000</v>
+      </c>
+      <c r="G91" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6225,13 +8786,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6241,6 +8802,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6251,30 +8813,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
@@ -6287,21 +8854,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>218654000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>153760000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>325649000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>134596000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>128208000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>76839000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6310,21 +8878,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-173727000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-170613000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>-115744000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-99615000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-103798000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>-106665000</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6333,21 +8902,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-7003000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-1158000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-4031000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-4029000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-3985000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-23090000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6368,9 +8938,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>19175000</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6379,21 +8950,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>17226000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>18742000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-1000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>17133000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6402,21 +8974,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-41048000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-73885000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-45428000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-39751000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-28738000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>-26884000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6425,21 +8998,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>24100000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>16879000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>16974000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>25043000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>17641000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>25559000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6448,21 +9022,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>38112000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>10718000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>28710000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>29432000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>45040000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>10426000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6471,21 +9046,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>1045361000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>1123658000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>1092197000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>1056225000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>949943000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>874913000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6494,21 +9070,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>1123658000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>1092197000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>1056225000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>949943000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>874913000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>935026000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6517,21 +9094,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-3340000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>2247000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-1565000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-2877000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>6226000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-3289000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6540,21 +9118,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>-74957000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>29214000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>37537000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>109159000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>68804000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>-56824000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6563,21 +9142,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-180730000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-154545000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-119773000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-84902000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-107786000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>-93457000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6586,21 +9166,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-180730000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-154545000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-119773000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-84902000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-107786000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>-93457000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6609,19 +9190,20 @@
         </is>
       </c>
       <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="n">
         <v>-2000</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="G16" s="3" t="n">
         <v>-10000</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="H16" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6632,21 +9214,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>-173727000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>-153387000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>-115742000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>-80873000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>-103799000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>-89532000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6655,21 +9238,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-173727000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-170613000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-115744000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>-99615000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-103798000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>-106665000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6678,21 +9262,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>17226000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>18742000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-1000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>17133000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6701,21 +9286,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-7003000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>-1158000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>-4031000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-4029000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-3985000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>-3915000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6724,21 +9310,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-7003000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>-1158000</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>-4031000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-4029000</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-3985000</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>-3915000</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6747,21 +9334,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-7003000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-1158000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-4031000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-4029000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-3985000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>-23090000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6782,9 +9370,10 @@
         <v>0</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>19175000</v>
+        <v>0</v>
       </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6793,21 +9382,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-153929000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-43886000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-213767000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>19714000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>19644000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>-67090000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6816,21 +9406,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-153929000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-43886000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-213767000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>19714000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>19644000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>-67090000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6839,21 +9430,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-112881000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>29999000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>62761000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>59465000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>48382000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>-40206000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6862,21 +9454,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>73962000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>69918000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>86968000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>94333000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>110460000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>56818000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6885,21 +9478,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>-186843000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-39919000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>-24207000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>-34868000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>-62078000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>-97024000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6908,15 +9502,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n">
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n">
         <v>-231100000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E29" s="3" t="n"/>
       <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n">
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n">
         <v>21682000</v>
       </c>
     </row>
@@ -6927,15 +9522,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n">
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n">
         <v>-231100000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n">
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n">
         <v>21682000</v>
       </c>
     </row>
@@ -6946,21 +9542,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-41048000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-73885000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-45428000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-39751000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>-28738000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>-26884000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6969,21 +9566,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-41048000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>-73885000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>-45428000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>-39751000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>-28738000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>-26884000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6992,21 +9590,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>259702000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>227645000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>371077000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>174347000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>156946000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>103723000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7015,21 +9614,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>259702000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>227645000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>371077000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>174347000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>156946000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>103723000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7038,21 +9638,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>-86979000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>-37724000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>154284000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>31836000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>41702000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>-7987000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7061,21 +9662,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>-50571000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>86013000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>25514000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>-28247000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>46182000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>20311000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7084,21 +9686,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>-3346000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>-3911000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>-4015000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>-3882000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>-3625000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>-4361000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7107,21 +9710,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>2470000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>2879000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>2854000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>3179000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>2678000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>2902000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7130,21 +9734,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>102962000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>-130907000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>143132000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>100109000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>32822000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>-49577000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7153,21 +9758,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>102962000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>-130907000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>143132000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>100109000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>32822000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>-49577000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7176,21 +9782,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>102962000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>-130907000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>143132000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>100109000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>32822000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>-49577000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7199,21 +9806,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>-74071000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>40024000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>-51236000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>53296000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>-7892000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>92036000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7222,21 +9830,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>16538000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>-41228000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>19891000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>3411000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>-41060000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>-35844000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7245,21 +9854,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>-80961000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>9406000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>18144000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>-96030000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>12597000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>-33454000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7268,21 +9878,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>-80961000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>9406000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>18144000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>-96030000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>12597000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>-33454000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7291,21 +9902,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>2148000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>-1545000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>90202000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>4517000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>300000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>-6655000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7314,21 +9926,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>55473000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>49827000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>48829000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>46929000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>47961000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>40806000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7337,21 +9950,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>29149000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>30017000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>22379000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>16342000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>17530000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>16615000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7360,21 +9974,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>-3520000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>-7043000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>-1464000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>-11239000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>6615000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>-17085000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7383,21 +9998,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>-3520000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>-7043000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>-1464000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>-11239000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>6615000</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>-17085000</v>
-      </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7406,21 +10022,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>45211000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>43830000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>37358000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>35654000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>33869000</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>33457000</v>
-      </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7429,21 +10046,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>45211000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>43830000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>37358000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>35654000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>33869000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>33457000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7452,21 +10070,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>10499000</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>11521000</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="D53" s="3" t="n">
         <v>9862000</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>8788000</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="F53" s="3" t="n">
         <v>8777000</v>
       </c>
-      <c r="F53" s="3" t="n">
-        <v>8778000</v>
-      </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7475,21 +10094,22 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
+        <v>10499000</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>11521000</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>9862000</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>8788000</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="F54" s="3" t="n">
         <v>8777000</v>
       </c>
-      <c r="F54" s="3" t="n">
-        <v>8778000</v>
-      </c>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7498,21 +10118,22 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
+        <v>34712000</v>
+      </c>
+      <c r="C55" s="3" t="n">
         <v>32309000</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="D55" s="3" t="n">
         <v>27496000</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>26866000</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="F55" s="3" t="n">
         <v>25092000</v>
       </c>
-      <c r="F55" s="3" t="n">
-        <v>24679000</v>
-      </c>
       <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7525,7 +10146,8 @@
       <c r="D56" s="3" t="n"/>
       <c r="E56" s="3" t="n"/>
       <c r="F56" s="3" t="n"/>
-      <c r="G56" s="3" t="n">
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7536,28 +10158,29 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
+        <v>218220000</v>
+      </c>
+      <c r="C57" s="3" t="n">
         <v>150283000</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="D57" s="3" t="n">
         <v>19489000</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="E57" s="3" t="n">
         <v>50308000</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="F57" s="3" t="n">
         <v>8969000</v>
       </c>
-      <c r="F57" s="3" t="n">
-        <v>44572000</v>
-      </c>
       <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
